--- a/outputs/Pulses_tukey_classification_matrix.xlsx
+++ b/outputs/Pulses_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="110">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,52 +343,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>15%</t>
   </si>
 </sst>
 </file>
@@ -1057,25 +1012,25 @@
         <v>108</v>
       </c>
       <c r="T2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA2" t="s">
         <v>108</v>
@@ -1216,13 +1171,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1284,28 +1239,28 @@
         <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
         <v>108</v>
@@ -1314,25 +1269,25 @@
         <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
         <v>108</v>
       </c>
       <c r="AJ3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK3" t="s">
         <v>108</v>
@@ -1443,13 +1398,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1511,31 +1466,31 @@
         <v>108</v>
       </c>
       <c r="T4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z4" t="s">
         <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
         <v>108</v>
@@ -1556,13 +1511,13 @@
         <v>108</v>
       </c>
       <c r="AI4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL4" t="s">
         <v>108</v>
@@ -1670,13 +1625,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BW4" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1741,7 +1696,7 @@
         <v>108</v>
       </c>
       <c r="U5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V5" t="s">
         <v>108</v>
@@ -1759,10 +1714,10 @@
         <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
         <v>108</v>
@@ -1771,7 +1726,7 @@
         <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
         <v>108</v>
@@ -1897,13 +1852,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2007,19 +1962,19 @@
         <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s">
         <v>108</v>
@@ -2124,13 +2079,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2351,13 +2306,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2425,43 +2380,43 @@
         <v>108</v>
       </c>
       <c r="V8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="s">
         <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
         <v>108</v>
@@ -2473,10 +2428,10 @@
         <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN8" t="s">
         <v>108</v>
@@ -2578,13 +2533,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2652,7 +2607,7 @@
         <v>108</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
         <v>108</v>
@@ -2673,7 +2628,7 @@
         <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
         <v>108</v>
@@ -2682,13 +2637,13 @@
         <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI9" t="s">
         <v>108</v>
@@ -2805,13 +2760,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW9" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2936,10 +2891,10 @@
         <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ10" t="s">
         <v>108</v>
@@ -3032,13 +2987,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3115,10 +3070,10 @@
         <v>108</v>
       </c>
       <c r="Y11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA11" t="s">
         <v>108</v>
@@ -3259,13 +3214,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3396,7 +3351,7 @@
         <v>108</v>
       </c>
       <c r="AQ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR12" t="s">
         <v>108</v>
@@ -3486,13 +3441,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV12" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW12" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3617,10 +3572,10 @@
         <v>108</v>
       </c>
       <c r="AO13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ13" t="s">
         <v>108</v>
@@ -3713,13 +3668,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW13" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3940,13 +3895,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4167,13 +4122,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4394,13 +4349,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4501,10 +4456,10 @@
         <v>108</v>
       </c>
       <c r="AG17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI17" t="s">
         <v>108</v>
@@ -4528,7 +4483,7 @@
         <v>108</v>
       </c>
       <c r="AP17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ17" t="s">
         <v>108</v>
@@ -4621,13 +4576,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV17" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW17" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4707,37 +4662,37 @@
         <v>108</v>
       </c>
       <c r="Z18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
         <v>108</v>
@@ -4848,13 +4803,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW18" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4994,49 +4949,49 @@
         <v>108</v>
       </c>
       <c r="AT19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW19" t="s">
         <v>108</v>
       </c>
       <c r="AX19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BC19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BE19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BI19" t="s">
         <v>108</v>
@@ -5075,13 +5030,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BV19" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5146,25 +5101,25 @@
         <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
         <v>108</v>
@@ -5302,13 +5257,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV20" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW20" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5400,13 +5355,13 @@
         <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
         <v>108</v>
       </c>
       <c r="AF21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s">
         <v>108</v>
@@ -5415,10 +5370,10 @@
         <v>108</v>
       </c>
       <c r="AI21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK21" t="s">
         <v>108</v>
@@ -5529,13 +5484,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5633,25 +5588,25 @@
         <v>108</v>
       </c>
       <c r="AF22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s">
         <v>108</v>
@@ -5756,13 +5711,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV22" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW22" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5866,7 +5821,7 @@
         <v>108</v>
       </c>
       <c r="AH23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI23" t="s">
         <v>108</v>
@@ -5887,10 +5842,10 @@
         <v>108</v>
       </c>
       <c r="AO23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ23" t="s">
         <v>108</v>
@@ -5983,13 +5938,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BW23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6210,13 +6165,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV24" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW24" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6347,7 +6302,7 @@
         <v>108</v>
       </c>
       <c r="AQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR25" t="s">
         <v>108</v>
@@ -6437,13 +6392,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV25" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW25" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6631,7 +6586,7 @@
         <v>108</v>
       </c>
       <c r="BJ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK26" t="s">
         <v>108</v>
@@ -6664,13 +6619,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV26" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW26" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6891,13 +6846,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6995,10 +6950,10 @@
         <v>108</v>
       </c>
       <c r="AF28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH28" t="s">
         <v>108</v>
@@ -7007,13 +6962,13 @@
         <v>108</v>
       </c>
       <c r="AJ28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM28" t="s">
         <v>108</v>
@@ -7118,13 +7073,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV28" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7225,28 +7180,28 @@
         <v>108</v>
       </c>
       <c r="AG29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
         <v>108</v>
       </c>
       <c r="AN29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO29" t="s">
         <v>108</v>
@@ -7345,13 +7300,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV29" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BW29" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7452,7 +7407,7 @@
         <v>108</v>
       </c>
       <c r="AG30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH30" t="s">
         <v>108</v>
@@ -7572,13 +7527,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV30" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW30" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7649,10 +7604,10 @@
         <v>108</v>
       </c>
       <c r="W31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y31" t="s">
         <v>108</v>
@@ -7709,7 +7664,7 @@
         <v>108</v>
       </c>
       <c r="AQ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR31" t="s">
         <v>108</v>
@@ -7799,13 +7754,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV31" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW31" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7864,25 +7819,25 @@
         <v>108</v>
       </c>
       <c r="S32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W32" t="s">
         <v>108</v>
       </c>
       <c r="X32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z32" t="s">
         <v>108</v>
@@ -8026,13 +7981,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV32" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BW32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8253,13 +8208,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV33" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW33" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8267,10 +8222,10 @@
         <v>107</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>108</v>
@@ -8390,10 +8345,10 @@
         <v>108</v>
       </c>
       <c r="AQ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS34" t="s">
         <v>108</v>
@@ -8480,13 +8435,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV34" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BW34" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Pulses_tukey_classification_matrix.xlsx
+++ b/outputs/Pulses_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
